--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/reference_taxa_clusters.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/reference_taxa_clusters.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,17 +697,17 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>019B</t>
+          <t>026C</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D5" t="n">
-        <v>1.503278703127448</v>
+        <v>3.55019708256048</v>
       </c>
       <c r="E5" t="n">
         <v>3.203426503814917e-16</v>
@@ -716,10 +716,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G5" t="n">
-        <v>5.922031955645113</v>
+        <v>2.192645077942396</v>
       </c>
       <c r="H5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.988684686772165</v>
       </c>
       <c r="I5" t="n">
         <v>3.203426503814917e-16</v>
@@ -731,16 +731,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L5" t="n">
-        <v>2.223337521298769</v>
+        <v>1.478047296804644</v>
       </c>
       <c r="M5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="N5" t="n">
-        <v>3.88376428594652</v>
+        <v>1.478047296804644</v>
       </c>
       <c r="O5" t="n">
-        <v>4.466034353461545</v>
+        <v>3.025535092107138</v>
       </c>
       <c r="P5" t="n">
         <v>3.203426503814917e-16</v>
@@ -749,13 +749,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R5" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.668378508908793</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>026C</t>
+          <t>030ABC</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -765,7 +765,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D6" t="n">
-        <v>3.55019708256048</v>
+        <v>4.045233364735362</v>
       </c>
       <c r="E6" t="n">
         <v>3.203426503814917e-16</v>
@@ -774,10 +774,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.192645077942396</v>
+        <v>1.264986512097531</v>
       </c>
       <c r="H6" t="n">
-        <v>5.988684686772165</v>
+        <v>6.309004397742273</v>
       </c>
       <c r="I6" t="n">
         <v>3.203426503814917e-16</v>
@@ -789,16 +789,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L6" t="n">
-        <v>1.478047296804644</v>
+        <v>1.68511366861321</v>
       </c>
       <c r="M6" t="n">
-        <v>3.025535092107138</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N6" t="n">
-        <v>1.478047296804644</v>
+        <v>0.8579075100879084</v>
       </c>
       <c r="O6" t="n">
-        <v>3.025535092107138</v>
+        <v>1.471200911255877</v>
       </c>
       <c r="P6" t="n">
         <v>3.203426503814917e-16</v>
@@ -807,23 +807,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R6" t="n">
-        <v>2.668378508908793</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>030ABC</t>
+          <t>033ABC</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D7" t="n">
-        <v>4.045233364735362</v>
+        <v>1.5556469338966</v>
       </c>
       <c r="E7" t="n">
         <v>3.203426503814917e-16</v>
@@ -832,31 +832,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G7" t="n">
-        <v>1.264986512097531</v>
+        <v>5.635374126367335</v>
       </c>
       <c r="H7" t="n">
-        <v>6.309004397742273</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I7" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.76955288934522</v>
       </c>
       <c r="K7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7194478329081769</v>
       </c>
       <c r="L7" t="n">
-        <v>1.68511366861321</v>
+        <v>1.197301440373618</v>
       </c>
       <c r="M7" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8969065070358966</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8579075100879084</v>
+        <v>0.5170584362193528</v>
       </c>
       <c r="O7" t="n">
-        <v>1.471200911255877</v>
+        <v>5.368130103004817</v>
       </c>
       <c r="P7" t="n">
         <v>3.203426503814917e-16</v>
@@ -871,17 +871,17 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>033ABC</t>
+          <t>035C</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5556469338966</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="E8" t="n">
         <v>3.203426503814917e-16</v>
@@ -890,31 +890,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G8" t="n">
-        <v>5.635374126367335</v>
+        <v>2.526545814495834</v>
       </c>
       <c r="H8" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.13026410847607</v>
       </c>
       <c r="I8" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J8" t="n">
-        <v>2.76955288934522</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7194478329081769</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L8" t="n">
-        <v>1.197301440373618</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8969065070358966</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5170584362193528</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O8" t="n">
-        <v>5.368130103004817</v>
+        <v>3.689831618575111</v>
       </c>
       <c r="P8" t="n">
         <v>3.203426503814917e-16</v>
@@ -929,50 +929,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>035C</t>
+          <t>036C</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.438197784198078</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.203426503814917e-16</v>
+      </c>
+      <c r="O9" t="n">
         <v>3.934112064343543</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.526545814495834</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.13026410847607</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.689831618575111</v>
       </c>
       <c r="P9" t="n">
         <v>3.203426503814917e-16</v>
@@ -987,17 +987,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>036C</t>
+          <t>058C</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9047272710591775</v>
       </c>
       <c r="E10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1006,10 +1006,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G10" t="n">
-        <v>6.438197784198078</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="H10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.643280158288579</v>
       </c>
       <c r="I10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1021,16 +1021,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.09368399654834478</v>
       </c>
       <c r="M10" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N10" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.04760230704818257</v>
       </c>
       <c r="O10" t="n">
-        <v>3.934112064343543</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P10" t="n">
         <v>3.203426503814917e-16</v>
@@ -1045,7 +1045,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>043ABC</t>
+          <t>060B</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1055,7 +1055,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D11" t="n">
-        <v>5.487806189871804</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1064,10 +1064,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4650147144136517</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H11" t="n">
-        <v>5.739616035545461</v>
+        <v>6.643254941572279</v>
       </c>
       <c r="I11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1079,16 +1079,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L11" t="n">
-        <v>1.169707246013332</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M11" t="n">
-        <v>1.615725305729703</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N11" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="O11" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.029747343394052</v>
       </c>
       <c r="P11" t="n">
         <v>3.203426503814917e-16</v>
@@ -1103,29 +1103,29 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>058C</t>
+          <t>064B</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9047272710591775</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="E12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.02267182631393</v>
       </c>
       <c r="F12" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09368399654834478</v>
+        <v>5.887992562015887</v>
       </c>
       <c r="H12" t="n">
-        <v>6.643280158288579</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1134,19 +1134,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7526899464592227</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09368399654834478</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="M12" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04760230704818257</v>
+        <v>1.244803668756707</v>
       </c>
       <c r="O12" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.611075341040287</v>
       </c>
       <c r="P12" t="n">
         <v>3.203426503814917e-16</v>
@@ -1161,29 +1161,29 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>060B</t>
+          <t>066A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="D13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="E13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.721932779208732</v>
       </c>
       <c r="F13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.304671300699757</v>
       </c>
       <c r="H13" t="n">
-        <v>6.643254941572279</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1195,16 +1195,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="M13" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N13" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.827323338290201</v>
       </c>
       <c r="O13" t="n">
-        <v>1.029747343394052</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P13" t="n">
         <v>3.203426503814917e-16</v>
@@ -1219,26 +1219,26 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>064B</t>
+          <t>068B</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D14" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E14" t="n">
-        <v>5.02267182631393</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G14" t="n">
-        <v>5.887992562015887</v>
+        <v>6.051070184214275</v>
       </c>
       <c r="H14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1250,19 +1250,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7526899464592227</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L14" t="n">
-        <v>1.611075341040287</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M14" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N14" t="n">
-        <v>1.244803668756707</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O14" t="n">
-        <v>1.611075341040287</v>
+        <v>5.157604729806445</v>
       </c>
       <c r="P14" t="n">
         <v>3.203426503814917e-16</v>
@@ -1277,26 +1277,26 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>066A</t>
+          <t>073C</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D15" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E15" t="n">
-        <v>3.721932779208732</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G15" t="n">
-        <v>6.304671300699757</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="H15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1311,16 +1311,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L15" t="n">
-        <v>1.150242635580613</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M15" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N15" t="n">
-        <v>2.827323338290201</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O15" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.658211482751795</v>
       </c>
       <c r="P15" t="n">
         <v>3.203426503814917e-16</v>
@@ -1335,17 +1335,17 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>068B</t>
+          <t>109C</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.529467388129453</v>
       </c>
       <c r="D16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.776898533069642</v>
       </c>
       <c r="E16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1354,10 +1354,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G16" t="n">
-        <v>6.051070184214275</v>
+        <v>3.623018726983232</v>
       </c>
       <c r="H16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.255073120131111</v>
       </c>
       <c r="I16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1375,10 +1375,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N16" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.203555779323592</v>
       </c>
       <c r="O16" t="n">
-        <v>5.157604729806445</v>
+        <v>4.443256343088573</v>
       </c>
       <c r="P16" t="n">
         <v>3.203426503814917e-16</v>
@@ -1393,7 +1393,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>073C</t>
+          <t>121C</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1412,7 +1412,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.886132035441721</v>
       </c>
       <c r="H17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1421,7 +1421,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="J17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="K17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1433,10 +1433,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N17" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.861530062208643</v>
       </c>
       <c r="O17" t="n">
-        <v>6.658211482751795</v>
+        <v>3.48595249488999</v>
       </c>
       <c r="P17" t="n">
         <v>3.203426503814917e-16</v>
@@ -1451,7 +1451,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>098C</t>
+          <t>122B</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1470,19 +1470,19 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G18" t="n">
-        <v>5.930737337562887</v>
+        <v>4.402534852460246</v>
       </c>
       <c r="H18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.8042755291256324</v>
       </c>
       <c r="J18" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="K18" t="n">
-        <v>4.392317422778761</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="L18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1491,10 +1491,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N18" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>6.289812447870645</v>
       </c>
       <c r="O18" t="n">
-        <v>4.392317422778761</v>
+        <v>1.518873310263384</v>
       </c>
       <c r="P18" t="n">
         <v>3.203426503814917e-16</v>
@@ -1509,17 +1509,17 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>109C</t>
+          <t>125A</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1.529467388129453</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D19" t="n">
-        <v>4.776898533069642</v>
+        <v>3.582027209696609</v>
       </c>
       <c r="E19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1528,10 +1528,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G19" t="n">
-        <v>3.623018726983232</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="H19" t="n">
-        <v>2.255073120131111</v>
+        <v>6.452617933046574</v>
       </c>
       <c r="I19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1549,10 +1549,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N19" t="n">
-        <v>5.203555779323592</v>
+        <v>1.150242635580613</v>
       </c>
       <c r="O19" t="n">
-        <v>4.443256343088573</v>
+        <v>0.6868421147403698</v>
       </c>
       <c r="P19" t="n">
         <v>3.203426503814917e-16</v>
@@ -1567,50 +1567,50 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>121C</t>
+          <t>133B</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="D20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.441858732844736</v>
       </c>
       <c r="E20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="F20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.399421886369236</v>
       </c>
       <c r="G20" t="n">
-        <v>4.886132035441721</v>
+        <v>4.592516646115072</v>
       </c>
       <c r="H20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.3657782510295</v>
       </c>
       <c r="I20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.186447986673725</v>
       </c>
       <c r="J20" t="n">
-        <v>2.345292087952873</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="K20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9685979008608663</v>
       </c>
       <c r="M20" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N20" t="n">
-        <v>5.861530062208643</v>
+        <v>3.28864350317529</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48595249488999</v>
+        <v>4.648634242809477</v>
       </c>
       <c r="P20" t="n">
         <v>3.203426503814917e-16</v>
@@ -1619,13 +1619,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R20" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5641038958234921</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>122B</t>
+          <t>139B</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1635,22 +1635,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="E21" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.195861790625938</v>
       </c>
       <c r="F21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G21" t="n">
-        <v>4.402534852460246</v>
+        <v>3.934112064343543</v>
       </c>
       <c r="H21" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8042755291256324</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1665,10 +1665,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N21" t="n">
-        <v>6.289812447870645</v>
+        <v>2.345292087952873</v>
       </c>
       <c r="O21" t="n">
-        <v>1.518873310263384</v>
+        <v>6.137252569345645</v>
       </c>
       <c r="P21" t="n">
         <v>3.203426503814917e-16</v>
@@ -1683,17 +1683,17 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>125A</t>
+          <t>S100</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D22" t="n">
-        <v>3.582027209696609</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1702,10 +1702,10 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6868421147403698</v>
+        <v>3.225220681487266</v>
       </c>
       <c r="H22" t="n">
-        <v>6.452617933046574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1723,16 +1723,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.150242635580613</v>
+        <v>4.82031925463496</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6868421147403698</v>
+        <v>6.021391865052195</v>
       </c>
       <c r="P22" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.525628361338754</v>
       </c>
       <c r="R22" t="n">
         <v>3.203426503814917e-16</v>
@@ -1741,32 +1741,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>133B</t>
+          <t>S101</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D23" t="n">
-        <v>4.441858732844736</v>
+        <v>3.68332477441813</v>
       </c>
       <c r="E23" t="n">
-        <v>0.399421886369236</v>
+        <v>2.373282005376731</v>
       </c>
       <c r="F23" t="n">
-        <v>0.399421886369236</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="G23" t="n">
-        <v>4.592516646115072</v>
+        <v>1.921229298351621</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3657782510295</v>
+        <v>6.178487014945737</v>
       </c>
       <c r="I23" t="n">
-        <v>1.186447986673725</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1775,16 +1775,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9685979008608663</v>
+        <v>2.048197292966219</v>
       </c>
       <c r="M23" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.259259362142412</v>
       </c>
       <c r="N23" t="n">
-        <v>3.28864350317529</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="O23" t="n">
-        <v>4.648634242809477</v>
+        <v>2.164889411545014</v>
       </c>
       <c r="P23" t="n">
         <v>3.203426503814917e-16</v>
@@ -1793,13 +1793,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5641038958234921</v>
+        <v>1.455312898831799</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>139B</t>
+          <t>S102</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1809,22 +1809,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D24" t="n">
-        <v>2.345292087952873</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="E24" t="n">
-        <v>3.195861790625938</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="F24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G24" t="n">
-        <v>3.934112064343543</v>
+        <v>1.268105395381216</v>
       </c>
       <c r="H24" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.7691161177699127</v>
       </c>
       <c r="J24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1836,13 +1836,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>3.914995645245574</v>
       </c>
       <c r="N24" t="n">
-        <v>2.345292087952873</v>
+        <v>6.369643421843278</v>
       </c>
       <c r="O24" t="n">
-        <v>6.137252569345645</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="P24" t="n">
         <v>3.203426503814917e-16</v>
@@ -1851,20 +1851,20 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R24" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.268105395381216</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>150B</t>
+          <t>S81</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>0.82797653267369</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="D25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1876,7 +1876,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G25" t="n">
-        <v>1.350716518311988</v>
+        <v>5.872231802852783</v>
       </c>
       <c r="H25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1897,16 +1897,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N25" t="n">
-        <v>2.285688951456035</v>
+        <v>3.87148525947732</v>
       </c>
       <c r="O25" t="n">
-        <v>6.56679155955111</v>
+        <v>4.741875508290013</v>
       </c>
       <c r="P25" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.330645311988472</v>
       </c>
       <c r="R25" t="n">
         <v>3.203426503814917e-16</v>
@@ -1915,14 +1915,14 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>S100</t>
+          <t>S82</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.9585800726200192</v>
       </c>
       <c r="D26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1934,7 +1934,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G26" t="n">
-        <v>3.225220681487266</v>
+        <v>4.312369266462518</v>
       </c>
       <c r="H26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1949,22 +1949,22 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L26" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.515253528909752</v>
       </c>
       <c r="M26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N26" t="n">
-        <v>4.82031925463496</v>
+        <v>4.090661722917659</v>
       </c>
       <c r="O26" t="n">
-        <v>6.021391865052195</v>
+        <v>5.917287628211485</v>
       </c>
       <c r="P26" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.525628361338754</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="R26" t="n">
         <v>3.203426503814917e-16</v>
@@ -1973,32 +1973,32 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>S101</t>
+          <t>S93</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D27" t="n">
-        <v>3.68332477441813</v>
+        <v>2.782901878333065</v>
       </c>
       <c r="E27" t="n">
-        <v>2.373282005376731</v>
+        <v>5.586729426895344</v>
       </c>
       <c r="F27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G27" t="n">
-        <v>1.921229298351621</v>
+        <v>2.782901878333065</v>
       </c>
       <c r="H27" t="n">
-        <v>6.178487014945737</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="I27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.782901878333065</v>
       </c>
       <c r="J27" t="n">
         <v>3.203426503814917e-16</v>
@@ -2007,31 +2007,31 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L27" t="n">
-        <v>2.048197292966219</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M27" t="n">
-        <v>1.259259362142412</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>2.782901878333065</v>
       </c>
       <c r="O27" t="n">
-        <v>2.164889411545014</v>
+        <v>2.782901878333065</v>
       </c>
       <c r="P27" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>4.616440732194325</v>
       </c>
       <c r="R27" t="n">
-        <v>1.455312898831799</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>S96</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2041,7 +2041,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="E28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2050,13 +2050,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G28" t="n">
-        <v>1.268105395381216</v>
+        <v>5.317915032380739</v>
       </c>
       <c r="H28" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7691161177699127</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="J28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2068,13 +2068,13 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="M28" t="n">
-        <v>3.914995645245574</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="N28" t="n">
-        <v>6.369643421843278</v>
+        <v>3.598259323334614</v>
       </c>
       <c r="O28" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>5.672425341971495</v>
       </c>
       <c r="P28" t="n">
         <v>3.203426503814917e-16</v>
@@ -2083,23 +2083,23 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.268105395381216</v>
+        <v>3.203426503814917e-16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>S81</t>
+          <t>S97</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1.330645311988472</v>
+        <v>1.34845438939755</v>
       </c>
       <c r="D29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>0.5997595026492368</v>
       </c>
       <c r="E29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2108,7 +2108,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G29" t="n">
-        <v>5.872231802852783</v>
+        <v>3.038523071803344</v>
       </c>
       <c r="H29" t="n">
         <v>3.203426503814917e-16</v>
@@ -2129,32 +2129,32 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N29" t="n">
-        <v>3.87148525947732</v>
+        <v>3.126305317145071</v>
       </c>
       <c r="O29" t="n">
-        <v>4.741875508290013</v>
+        <v>6.203209230748278</v>
       </c>
       <c r="P29" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.330645311988472</v>
+        <v>3.126305317145071</v>
       </c>
       <c r="R29" t="n">
-        <v>3.203426503814917e-16</v>
+        <v>1.838879010391133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>S82</t>
+          <t>S99</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9585800726200192</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="D30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2166,7 +2166,7 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="G30" t="n">
-        <v>4.312369266462518</v>
+        <v>2.493040011280117</v>
       </c>
       <c r="H30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2181,16 +2181,16 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="L30" t="n">
-        <v>2.515253528909752</v>
+        <v>3.203426503814917e-16</v>
       </c>
       <c r="M30" t="n">
         <v>3.203426503814917e-16</v>
       </c>
       <c r="N30" t="n">
-        <v>4.090661722917659</v>
+        <v>2.233797184608697</v>
       </c>
       <c r="O30" t="n">
-        <v>5.917287628211485</v>
+        <v>6.533978572002351</v>
       </c>
       <c r="P30" t="n">
         <v>3.203426503814917e-16</v>
@@ -2199,238 +2199,6 @@
         <v>3.203426503814917e-16</v>
       </c>
       <c r="R30" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>S93</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2.782901878333065</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5.586729426895344</v>
-      </c>
-      <c r="F31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2.782901878333065</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I31" t="n">
-        <v>2.782901878333065</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.782901878333065</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.782901878333065</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.616440732194325</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>S96</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5.317915032380739</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3.598259323334614</v>
-      </c>
-      <c r="O32" t="n">
-        <v>5.672425341971495</v>
-      </c>
-      <c r="P32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>S97</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.34845438939755</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.5997595026492368</v>
-      </c>
-      <c r="E33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.038523071803344</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.126305317145071</v>
-      </c>
-      <c r="O33" t="n">
-        <v>6.203209230748278</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.126305317145071</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.838879010391133</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>S99</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.493040011280117</v>
-      </c>
-      <c r="H34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="I34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.233797184608697</v>
-      </c>
-      <c r="O34" t="n">
-        <v>6.533978572002351</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.203426503814917e-16</v>
-      </c>
-      <c r="R34" t="n">
         <v>3.203426503814917e-16</v>
       </c>
     </row>
